--- a/Caspar_etal_2022/Caspar_etal_2022_exportMSexcel.xlsx
+++ b/Caspar_etal_2022/Caspar_etal_2022_exportMSexcel.xlsx
@@ -42456,8 +42456,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -42481,8 +42481,6 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -42557,16 +42555,6 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -42731,7 +42719,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08905BB8-849D-4334-B193-BA89DFCF693C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7005054A-9FE8-49C1-B66A-9691D3C139BC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
